--- a/docs/ボディ見える化_PLCデバイス.xlsx
+++ b/docs/ボディ見える化_PLCデバイス.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\body_inspect_visualize_coba\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForCustomers\body_inspect_visualize_coba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CB3FFE-3D3F-4D4F-BFDD-2554B970C3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A05C586-B40B-455E-ACBD-73B4F5B2A9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4657B025-33E1-4D12-9C02-57E9F5466666}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4657B025-33E1-4D12-9C02-57E9F5466666}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
   <si>
     <t>機能</t>
     <rPh sb="0" eb="2">
@@ -339,10 +339,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>EM10092</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>使わない可能性高い</t>
     <rPh sb="0" eb="1">
       <t>ツカ</t>
@@ -502,6 +498,48 @@
     <rPh sb="12" eb="14">
       <t>サンショウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM4400-DM4403</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレイ内製品カウンタ(1W)</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1W x 4トレイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2W</t>
+  </si>
+  <si>
+    <t>EM10092</t>
+  </si>
+  <si>
+    <t>発生毎にインクリメント</t>
+  </si>
+  <si>
+    <t>1600個毎カウンタ</t>
+    <rPh sb="4" eb="6">
+      <t>コゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2W</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EM10094</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -609,7 +647,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -682,13 +720,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -734,12 +783,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -750,6 +793,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -825,13 +880,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>210353</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>187380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>440634</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>224588</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -875,9 +930,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -915,7 +970,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1021,7 +1076,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1163,7 +1218,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1174,7 +1229,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E34"/>
+  <dimension ref="B1:E40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1184,10 +1239,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D1" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="18">
+      <c r="D1" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="16">
         <v>46223</v>
       </c>
     </row>
@@ -1220,7 +1275,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
@@ -1236,34 +1291,34 @@
       <c r="E5" s="8"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="20" t="s">
+      <c r="E7" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B8" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>57</v>
@@ -1272,267 +1327,288 @@
         <v>58</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>59</v>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B9" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>85</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="57" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="2:5" ht="57" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="2:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="2:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B19" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C19" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D19" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="4" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="8"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="8"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="8"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B31" s="5"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B32" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="B32" s="5"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" t="s">
-        <v>74</v>
+      <c r="B33" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ボディ見える化_PLCデバイス.xlsx
+++ b/docs/ボディ見える化_PLCデバイス.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForCustomers\body_inspect_visualize_coba\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Kyowasv\共有ファイル\M-光和共有ファイル\P_個人用フォルダ(PersonalFolder)\F_間瀬文博\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A05C586-B40B-455E-ACBD-73B4F5B2A9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2518BE-98AA-4343-83E1-A13BFF6DA8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4657B025-33E1-4D12-9C02-57E9F5466666}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
   <si>
     <t>機能</t>
     <rPh sb="0" eb="2">
@@ -540,6 +540,38 @@
   </si>
   <si>
     <t>EM10094</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EM10126</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EM10226</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10/12の週でPLC変更</t>
+    <rPh sb="6" eb="7">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(PCは10/11)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4ST ボトム厚(演算)</t>
+    <rPh sb="7" eb="8">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>エンザン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -647,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -731,13 +763,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -805,6 +846,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -930,9 +974,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -970,7 +1014,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1076,7 +1120,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1218,7 +1262,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1570,8 +1614,25 @@
       </c>
       <c r="E30" s="8"/>
     </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B31" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>92</v>
+      </c>
+    </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="5"/>
+      <c r="E32" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
